--- a/events/Bratislava_2021_WCH/Bratislava_2021_WCH_start.xlsx
+++ b/events/Bratislava_2021_WCH/Bratislava_2021_WCH_start.xlsx
@@ -29552,6 +29552,11 @@
           <t>APEL Elena</t>
         </is>
       </c>
+      <c r="X481" t="inlineStr">
+        <is>
+          <t>51837</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -29610,6 +29615,11 @@
           <t>STACH Aleksandra</t>
         </is>
       </c>
+      <c r="X482" t="inlineStr">
+        <is>
+          <t>61261</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -32125,6 +32135,11 @@
           <t>MUTURI Samuel</t>
         </is>
       </c>
+      <c r="X522" t="inlineStr">
+        <is>
+          <t>68743</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -49363,6 +49378,11 @@
           <t>STACH Aleksandra</t>
         </is>
       </c>
+      <c r="X808" t="inlineStr">
+        <is>
+          <t>61261</t>
+        </is>
+      </c>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">
@@ -49736,6 +49756,11 @@
           <t>APEL Elena</t>
         </is>
       </c>
+      <c r="X814" t="inlineStr">
+        <is>
+          <t>51837</t>
+        </is>
+      </c>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
@@ -51117,6 +51142,11 @@
           <t>MUTURI Samuel</t>
         </is>
       </c>
+      <c r="X836" t="inlineStr">
+        <is>
+          <t>68743</t>
+        </is>
+      </c>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
@@ -53002,6 +53032,11 @@
           <t>APEL Elena</t>
         </is>
       </c>
+      <c r="X866" t="inlineStr">
+        <is>
+          <t>51837</t>
+        </is>
+      </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
@@ -54761,6 +54796,11 @@
           <t>APEL Elena</t>
         </is>
       </c>
+      <c r="X894" t="inlineStr">
+        <is>
+          <t>51837</t>
+        </is>
+      </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
@@ -55520,6 +55560,11 @@
       <c r="R906" t="inlineStr">
         <is>
           <t>APEL Elena</t>
+        </is>
+      </c>
+      <c r="X906" t="inlineStr">
+        <is>
+          <t>51837</t>
         </is>
       </c>
     </row>
